--- a/devPRs/dependabot[bot]_prs.xlsx
+++ b/devPRs/dependabot[bot]_prs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,11 +445,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1595</v>
+        <v>4382</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-06-12T21:55:22+00:00</t>
+          <t>2026-07-01T20:17:34+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -460,17 +460,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bump braces and gulp</t>
+          <t>chore(deps): bump sigstore from 4.0.0 to 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1594</v>
+        <v>4381</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-05-02T02:26:24+00:00</t>
+          <t>2026-06-30T13:27:22+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -481,45 +481,41 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bump ejs from 3.1.8 to 3.1.10</t>
+          <t>chore(deps): bump @sigstore/core from 3.0.0 to 3.2.1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1593</v>
+        <v>4377</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03-16T22:50:42+00:00</t>
+          <t>2026-06-22T12:20:29+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bump follow-redirects from 1.15.4 to 1.15.6</t>
+          <t>chore(deps): bump webpack-dev-server from 5.2.3 to 5.2.5 in /website</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1585</v>
+        <v>4376</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-09T17:30:15+00:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2024-01-10T10:48:03+00:00</t>
-        </is>
-      </c>
+          <t>2026-06-22T12:20:13+00:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>closed</t>
@@ -527,45 +523,41 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bump follow-redirects from 1.14.8 to 1.15.4</t>
+          <t>chore(deps): bump js-yaml from 4.1.1 to 4.2.0 in /packages/lerna</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1580</v>
+        <v>4375</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-11-10T16:16:41+00:00</t>
+          <t>2026-06-22T12:20:11+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bump axios and @11ty/eleventy</t>
+          <t>chore(deps): bump tar from 7.5.11 to 7.5.16 in /packages/lerna</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1577</v>
+        <v>4374</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-10-17T12:51:14+00:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2023-10-17T12:58:50+00:00</t>
-        </is>
-      </c>
+          <t>2026-06-22T05:31:12+00:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>closed</t>
@@ -573,24 +565,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bump socket.io-parser and socket.io</t>
+          <t>chore(deps): bump ws in /website</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1576</v>
+        <v>4373</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-10-17T11:18:00+00:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2023-10-17T12:50:12+00:00</t>
-        </is>
-      </c>
+          <t>2026-06-21T18:01:41+00:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>closed</t>
@@ -598,17 +586,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bump @babel/traverse from 7.16.3 to 7.23.2</t>
+          <t>chore(deps): bump form-data from 4.0.5 to 4.0.6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1568</v>
+        <v>4372</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023-07-07T20:58:11+00:00</t>
+          <t>2026-06-19T15:28:45+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -619,17 +607,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bump stylelint from 13.13.1 to 15.10.1</t>
+          <t>chore(deps): bump launch-editor from 2.13.1 to 2.14.1 in /website</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1557</v>
+        <v>4371</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023-05-23T23:13:36+00:00</t>
+          <t>2026-06-15T17:59:47+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -640,45 +628,41 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bump socket.io-parser and socket.io</t>
+          <t>chore(deps): bump js-yaml from 4.1.1 to 4.2.0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1549</v>
+        <v>4370</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023-05-04T00:56:02+00:00</t>
+          <t>2026-06-13T04:50:33+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bump engine.io and socket.io</t>
+          <t>chore(deps-dev): bump esbuild from 0.25.8 to 0.28.1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1547</v>
+        <v>4367</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023-04-20T21:43:31+00:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2023-04-21T03:06:35+00:00</t>
-        </is>
-      </c>
+          <t>2026-06-09T17:29:12+00:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>closed</t>
@@ -686,17 +670,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bump nunjucks from 3.2.3 to 3.2.4</t>
+          <t>chore(deps): bump shell-quote from 1.8.3 to 1.8.4 in /website</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1546</v>
+        <v>4366</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023-04-15T01:08:48+00:00</t>
+          <t>2026-06-05T16:49:05+00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -707,24 +691,20 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bump liquidjs and @11ty/eleventy</t>
+          <t>chore(deps): bump axios from 1.13.5 to 1.17.0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1545</v>
+        <v>4364</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2023-04-15T01:08:32+00:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2023-04-20T06:23:27+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-29T21:27:08+00:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>closed</t>
@@ -732,24 +712,20 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bump ua-parser-js and browser-sync</t>
+          <t>chore(deps): bump axios from 1.13.5 to 1.16.1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1504</v>
+        <v>4363</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2023-01-09T14:26:25+00:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2023-01-18T01:04:06+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-28T03:16:05+00:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>closed</t>
@@ -757,24 +733,20 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bump luxon from 2.3.0 to 2.5.2</t>
+          <t>chore(deps): bump tmp from 0.2.5 to 0.2.7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1501</v>
+        <v>4361</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2023-01-05T01:21:47+00:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2023-01-05T01:26:20+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-22T19:06:36+00:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>closed</t>
@@ -782,24 +754,20 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bump qs and browser-sync</t>
+          <t>chore(deps): bump qs and express in /website</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1500</v>
+        <v>4360</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2023-01-05T01:21:38+00:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2023-01-05T01:26:12+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-18T17:30:58+00:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>closed</t>
@@ -807,24 +775,20 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bump json5 from 2.2.0 to 2.2.3</t>
+          <t>chore(deps): bump webpack-dev-server from 5.2.3 to 5.2.4 in /website</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1493</v>
+        <v>4359</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2022-12-07T04:31:07+00:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2022-12-07T16:21:21+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-16T13:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>closed</t>
@@ -832,24 +796,20 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bump decode-uri-component from 0.2.0 to 0.2.2</t>
+          <t>chore(deps): bump fast-uri from 3.1.0 to 3.1.2 in /website</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1489</v>
+        <v>4356</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2022-11-22T16:05:17+00:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2022-11-22T16:09:25+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-09T17:40:57+00:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>closed</t>
@@ -857,24 +817,20 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bump @xmldom/xmldom from 0.8.3 to 0.8.6</t>
+          <t>chore(deps): bump @babel/plugin-transform-modules-systemjs from 7.29.0 to 7.29.4 in /website</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1488</v>
+        <v>4355</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2022-11-22T06:08:15+00:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2022-11-22T16:04:40+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-08T20:35:32+00:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>closed</t>
@@ -882,24 +838,20 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bump engine.io from 6.2.0 to 6.2.1</t>
+          <t>chore(deps): bump @babel/plugin-transform-modules-systemjs from 7.24.1 to 7.29.4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1487</v>
+        <v>4354</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2022-11-10T07:17:05+00:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2023-01-05T01:21:06+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-08T20:10:09+00:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>closed</t>
@@ -907,24 +859,20 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bump minimatch from 3.0.4 to 3.0.8</t>
+          <t>chore(deps): bump fast-uri from 3.1.0 to 3.1.2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1483</v>
+        <v>4353</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2022-10-17T22:29:32+00:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2022-10-17T22:30:48+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-08T00:57:43+00:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>closed</t>
@@ -932,24 +880,20 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bump nth-check and gulp-svg-sprite</t>
+          <t>chore(deps): bump axios from 1.13.5 to 1.16.0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1482</v>
+        <v>4352</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2022-10-17T22:29:06+00:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2022-10-17T22:30:21+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-08T00:46:25+00:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>closed</t>
@@ -957,24 +901,20 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bump shelljs and jshint</t>
+          <t>chore(deps): bump postcss from 8.5.6 to 8.5.14 in /website</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1481</v>
+        <v>4351</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2022-10-17T22:27:05+00:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2022-10-17T22:28:29+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-08T00:45:29+00:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>closed</t>
@@ -982,24 +922,20 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bump @xmldom/xmldom from 0.7.5 to 0.7.6</t>
+          <t>chore(deps): bump brace-expansion from 1.1.12 to 1.1.14 in /website</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1467</v>
+        <v>4350</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2022-08-17T00:46:23+00:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2022-08-17T00:47:50+00:00</t>
-        </is>
-      </c>
+          <t>2026-05-07T00:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>closed</t>
@@ -1007,24 +943,20 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bump highlight.js and kss</t>
+          <t>chore(deps): bump ip-address from 10.0.1 to 10.2.0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1465</v>
+        <v>4348</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2022-08-16T14:31:09+00:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2022-08-16T14:32:01+00:00</t>
-        </is>
-      </c>
+          <t>2026-04-15T18:50:11+00:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>closed</t>
@@ -1032,24 +964,20 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bump async from 2.6.3 to 2.6.4</t>
+          <t>chore(deps): bump follow-redirects from 1.15.11 to 1.16.0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1464</v>
+        <v>4347</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2022-08-16T14:28:22+00:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2022-08-17T00:44:21+00:00</t>
-        </is>
-      </c>
+          <t>2026-04-12T10:25:38+00:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>closed</t>
@@ -1057,24 +985,20 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bump minimist from 1.2.5 to 1.2.6</t>
+          <t>chore(deps): bump axios from 1.13.5 to 1.15.0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1463</v>
+        <v>4346</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2022-08-16T14:28:18+00:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2022-08-16T14:30:46+00:00</t>
-        </is>
-      </c>
+          <t>2026-04-10T03:26:21+00:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>closed</t>
@@ -1082,24 +1006,20 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bump json-schema from 0.2.3 to 0.4.0</t>
+          <t>chore(deps): bump lodash from 4.17.23 to 4.18.1 in /website</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1462</v>
+        <v>4338</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2022-08-16T14:28:17+00:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2022-08-16T14:30:34+00:00</t>
-        </is>
-      </c>
+          <t>2026-03-30T11:18:53+00:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>closed</t>
@@ -1107,24 +1027,20 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bump engine.io from 3.5.0 to 6.2.0</t>
+          <t>chore(deps): bump path-to-regexp from 0.1.12 to 0.1.13 in /website</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1453</v>
+        <v>4337</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2022-07-21T15:16:56+00:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2022-07-21T15:35:16+00:00</t>
-        </is>
-      </c>
+          <t>2026-03-30T03:33:58+00:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>closed</t>
@@ -1132,24 +1048,20 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bump ejs from 3.1.6 to 3.1.8</t>
+          <t>chore(deps): bump minimatch and serve-handler in /website</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1452</v>
+        <v>4336</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2022-07-21T15:16:53+00:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2022-07-21T15:35:02+00:00</t>
-        </is>
-      </c>
+          <t>2026-03-27T00:18:30+00:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>closed</t>
@@ -1157,47 +1069,43 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bump nanoid from 3.1.30 to 3.3.4</t>
+          <t>chore(deps): bump yaml</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1451</v>
+        <v>4335</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2022-07-20T19:34:44+00:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2022-07-21T15:16:13+00:00</t>
-        </is>
-      </c>
+          <t>2026-03-25T22:02:35+00:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bump terser from 5.10.0 to 5.14.2</t>
+          <t>chore(deps): bump picomatch from 2.3.1 to 2.3.2 in /website</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1418</v>
+        <v>4334</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2022-02-26T02:04:48+00:00</t>
+          <t>2026-03-21T10:28:39+00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2022-02-26T21:23:00+00:00</t>
+          <t>2026-03-23T12:50:35+00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1207,24 +1115,20 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bump prismjs from 1.26.0 to 1.27.0</t>
+          <t>chore(deps-dev): bump flatted from 3.3.3 to 3.4.2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1414</v>
+        <v>4297</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2022-02-13T21:12:32+00:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2022-02-13T21:59:36+00:00</t>
-        </is>
-      </c>
+          <t>2026-03-10T13:55:10+00:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>closed</t>
@@ -1232,24 +1136,20 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bump follow-redirects from 1.14.7 to 1.14.8</t>
+          <t>chore(deps): bump tar from 7.5.8 to 7.5.10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1401</v>
+        <v>4295</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2022-01-12T23:12:17+00:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2022-01-13T00:18:34+00:00</t>
-        </is>
-      </c>
+          <t>2026-03-10T13:54:08+00:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>closed</t>
@@ -1257,24 +1157,20 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bump markdown-it from 12.1.0 to 12.3.2</t>
+          <t>chore(deps): bump tar from 7.5.8 to 7.5.10 in /packages/legacy-structure/commands/create</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1245</v>
+        <v>4290</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2021-04-22T20:01:30+00:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2021-04-22T21:36:48+00:00</t>
-        </is>
-      </c>
+          <t>2026-03-05T00:09:19+00:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>closed</t>
@@ -1282,24 +1178,20 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bump y18n from 3.2.1 to 3.2.2</t>
+          <t>chore(deps): bump svgo from 3.3.2 to 3.3.3 in /website</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1199</v>
+        <v>4286</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2021-03-03T05:17:53+00:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2021-03-03T15:29:28+00:00</t>
-        </is>
-      </c>
+          <t>2026-02-28T07:24:52+00:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>closed</t>
@@ -1307,22 +1199,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bump pug-code-gen from 2.0.2 to 2.0.3</t>
+          <t>chore(deps): bump ajv from 6.12.6 to 6.14.0 in /website</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1168</v>
+        <v>4285</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2020-12-13T07:31:07+00:00</t>
+          <t>2026-02-28T02:11:32+00:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2020-12-13T21:07:10+00:00</t>
+          <t>2026-02-28T07:23:31+00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1332,7 +1224,2493 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bump ini from 1.3.5 to 1.3.8</t>
+          <t>fix: bump minimatch from 3.0.5 to 3.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4284</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-02-26T15:24:15+00:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>chore(deps): bump minimatch from 3.0.5 to 3.1.3 in /packages/lerna</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4283</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-02-24T23:06:33+00:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>chore(deps): bump minimatch from 3.0.5 to 3.1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4282</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-02-23T20:34:50+00:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>chore(deps): bump minimatch from 3.0.5 to 10.2.1 in /packages/lerna</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4280</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-02-22T19:54:54+00:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-02-28T08:40:31+00:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>chore(deps): bump qs and verdaccio</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4279</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-02-22T19:54:32+00:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>chore(deps): bump minimatch from 3.0.5 to 10.2.1 in /packages/legacy-structure/commands/create</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4278</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-02-22T13:03:30+00:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>chore(deps): bump ajv in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4276</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-02-20T12:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>chore(deps): bump qs and express in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4273</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-02-19T18:57:12+00:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-02-20T12:31:05+00:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>fix: bump tar from 7.5.7 to 7.5.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4272</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-02-19T18:44:37+00:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>chore(deps): bump minimatch from 3.0.5 to 10.2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4270</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-02-10T19:36:57+00:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-02-20T12:31:33+00:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>chore(deps): bump axios from 1.12.2 to 1.13.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4269</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-02-07T08:38:28+00:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>chore(deps): bump webpack from 5.95.0 to 5.105.0 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4268</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-01-28T16:46:17+00:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>chore(deps): bump tar from 6.2.1 to 7.5.7 in /packages/lerna</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4267</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-01-28T16:44:15+00:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-02-10T20:29:00+00:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>fix: bump tar to 7.5.7, rimraf to 6.1.2, @npmcli/run-script to 10.0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4266</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-01-28T16:40:15+00:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>chore(deps): bump tar from 6.2.1 to 7.5.7 in /packages/legacy-structure/commands/create</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4262</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-01-21T23:23:25+00:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>chore(deps): bump lodash from 4.17.21 to 4.17.23 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4261</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-01-21T01:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>chore(deps): bump tar from 6.2.1 to 7.5.4 in /packages/lerna</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4259</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-01-16T21:17:52+00:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>chore(deps): bump tar from 6.2.1 to 7.5.3 in /packages/legacy-structure/commands/create</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4256</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-01-01T21:49:14+00:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>chore(deps): bump node-forge from 1.3.1 to 1.3.3 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4255</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-01-01T13:34:41+00:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>chore(deps): bump qs and express in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4253</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-12-04T16:56:13+00:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-02-28T08:21:11+00:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>chore(deps): bump jws from 3.2.2 to 3.2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4252</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-12-02T03:38:12+00:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>chore(deps): bump mdast-util-to-hast from 13.2.0 to 13.2.1 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4251</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-11-27T17:18:59+00:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-02-10T19:35:00+00:00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>chore(deps): bump validator and verdaccio</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4250</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-11-26T22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>chore(deps): bump node-forge from 1.3.1 to 1.3.2 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4249</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-11-18T20:14:33+00:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>chore(deps): bump js-yaml from 3.14.1 to 3.14.2 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4248</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-11-18T16:57:24+00:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2025-11-27T17:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>chore(deps): bump glob from 10.4.5 to 10.5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4246</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-11-15T10:36:11+00:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>chore(deps): bump js-yaml from 4.1.0 to 4.1.1 in /packages/lerna</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4245</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-11-14T14:40:37+00:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2025-11-18T08:28:52+00:00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>chore(deps): bump js-yaml from 4.1.0 to 4.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4224</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-09-13T12:39:06+00:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2025-09-15T09:19:28+00:00</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>chore(deps): bump axios from 1.8.4 to 1.12.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4215</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-08-06T17:08:48+00:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2025-09-15T10:42:50+00:00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>chore(deps-dev): bump tmp from 0.2.3 to 0.2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4204</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-07-25T10:36:53+00:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>chore(deps): bump brace-expansion from 1.1.11 to 1.1.12 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4199</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-07-21T23:09:49+00:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2025-07-22T07:39:03+00:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>chore(deps): bump form-data from 4.0.0 to 4.0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4198</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-07-17T21:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>chore(deps): bump on-headers and compression in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4176</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-04-10T13:14:41+00:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>chore(deps): bump axios from 1.7.5 to 1.8.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4172</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-04-08T02:09:04+00:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>chore(deps): bump estree-util-value-to-estree from 3.1.2 to 3.3.3 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4171</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-04-02T15:07:18+00:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>chore(deps): bump image-size from 1.1.1 to 1.2.1 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4164</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-03-12T19:46:57+00:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>chore(deps): bump @babel/helpers from 7.23.9 to 7.26.10 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4163</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-03-12T19:46:56+00:00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>chore(deps): bump @babel/runtime from 7.23.9 to 7.26.10 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4162</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-03-12T19:46:39+00:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>chore(deps): bump semver from 5.7.1 to 5.7.2 in /libs/commands/version/__fixtures__/lockfile-v2-missing-local-deps/packages/package-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4160</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-03-11T20:54:22+00:00</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>chore(deps): bump @babel/runtime-corejs3 from 7.23.9 to 7.26.10 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4158</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-03-11T02:27:31+00:00</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>chore(deps): bump yargs-parser and yargs in /libs/commands/version/__fixtures__/lockfile-v2-missing-local-deps/packages/package-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4157</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-03-10T22:21:38+00:00</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>chore(deps): bump prismjs from 1.29.0 to 1.30.0 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4147</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-02-12T00:02:24+00:00</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>chore(deps-dev): bump esbuild from 0.21.5 to 0.25.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4136</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2024-12-14T15:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>chore(deps): bump nanoid from 3.3.7 to 3.3.8 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4132</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2024-12-06T00:59:21+00:00</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>chore(deps): bump path-to-regexp and express in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4125</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2024-11-20T05:43:35+00:00</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>chore(deps): bump cross-spawn from 7.0.3 to 7.0.6 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4102</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2024-10-30T13:04:31+00:00</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>chore(deps): bump send and express in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4101</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2024-10-30T13:04:12+00:00</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>chore(deps): bump express from 4.19.2 to 4.21.1 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4099</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2024-10-25T08:57:05+00:00</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>chore(deps): bump http-proxy-middleware from 2.0.6 to 2.0.7 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4083</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2024-09-21T11:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>chore(deps): bump body-parser and verdaccio</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4082</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2024-09-21T08:13:45+00:00</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>chore(deps): bump express and verdaccio</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4081</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2024-09-17T03:53:39+00:00</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2024-10-30T13:02:59+00:00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>chore(deps): bump send and verdaccio</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4080</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2024-09-17T03:24:54+00:00</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>chore(deps): bump serve-static and verdaccio</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4078</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2024-08-31T01:57:19+00:00</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>chore(deps): bump webpack from 5.90.1 to 5.94.0 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4073</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2024-08-26T15:26:56+00:00</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2024-08-26T16:20:31+00:00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>chore(deps): bump axios from 1.6.8 to 1.7.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4072</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2024-08-26T15:26:53+00:00</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2024-08-26T16:02:32+00:00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>chore(deps): bump micromatch from 4.0.5 to 4.0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4031</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2024-06-19T02:39:27+00:00</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>chore(deps-dev): bump ws from 8.17.0 to 8.17.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4028</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2024-06-16T09:53:14+00:00</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>chore(deps): bump braces from 3.0.2 to 3.0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4002</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2024-05-11T11:35:51+00:00</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2024-05-11T15:48:53+00:00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>chore(deps): bump express and verdaccio</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4000</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2024-05-10T18:58:35+00:00</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>chore(deps): bump tar from 6.1.11 to 6.2.1 in /packages/legacy-package-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>3999</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2024-05-10T18:58:34+00:00</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>chore(deps): bump tar from 6.1.11 to 6.2.1 in /packages/lerna</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>3994</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2024-05-02T11:07:04+00:00</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2024-05-11T15:48:23+00:00</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>chore(deps): bump ejs from 3.1.9 to 3.1.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>3990</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2024-04-11T00:39:08+00:00</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2024-05-11T11:34:10+00:00</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>chore(deps): bump tar from 6.1.11 to 6.2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>3984</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2024-03-28T15:25:50+00:00</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2024-05-11T20:04:25+00:00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>chore(deps): bump express from 4.18.2 to 4.19.2 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>3980</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2024-03-23T07:04:40+00:00</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>chore(deps): bump webpack-dev-middleware from 5.3.3 to 5.3.4 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>3977</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2024-03-16T23:58:06+00:00</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2024-03-18T09:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>chore(deps): bump follow-redirects from 1.15.5 to 1.15.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>3976</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2024-03-16T23:58:03+00:00</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>chore(deps): bump follow-redirects from 1.15.5 to 1.15.6 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>3960</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2024-02-20T18:48:27+00:00</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2024-03-08T15:50:41+00:00</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>chore(deps): bump ip from 2.0.0 to 2.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>3947</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2024-02-05T11:44:08+00:00</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>chore(deps): bump axios, @docusaurus/core, @docusaurus/plugin-sitemap and @docusaurus/preset-classic in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>3946</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2024-02-05T11:36:33+00:00</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2024-02-05T13:45:08+00:00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>chore(deps): bump follow-redirects from 1.15.3 to 1.15.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>3934</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2024-01-11T03:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>chore(deps): bump follow-redirects from 1.15.3 to 1.15.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>3932</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2024-01-10T01:09:30+00:00</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2024-02-05T11:35:17+00:00</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>chore(deps): bump follow-redirects from 1.15.1 to 1.15.4 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>3922</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2023-12-15T12:32:11+00:00</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>chore(deps-dev): bump the npm_and_yarn group group with 1 update</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>3920</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2023-12-15T10:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>chore(deps): bump tough-cookie and verdaccio</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>3900</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2023-11-15T16:19:29+00:00</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>chore(deps): bump axios, @docusaurus/core, @docusaurus/plugin-sitemap and @docusaurus/preset-classic in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>3898</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2023-11-11T16:19:07+00:00</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2023-11-15T16:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>chore(deps): bump axios from 1.5.1 to 1.6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>3896</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2023-11-09T08:25:03+00:00</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>chore(deps): bump got, @docusaurus/core, @docusaurus/plugin-sitemap and @docusaurus/preset-classic in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>3895</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2023-11-09T08:24:56+00:00</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>chore(deps): bump trim, @docusaurus/core, @docusaurus/plugin-sitemap and @docusaurus/preset-classic in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>3869</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2023-10-17T16:08:44+00:00</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2023-10-19T02:41:12+00:00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>chore(deps): bump @babel/traverse from 7.20.0 to 7.23.2 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>3857</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2023-10-07T07:32:37+00:00</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2023-10-09T20:54:16+00:00</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>chore(deps): bump postcss from 8.4.18 to 8.4.31 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>3786</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2023-07-18T20:10:19+00:00</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2023-07-24T14:34:20+00:00</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>chore(deps-dev): bump word-wrap from 1.2.3 to 1.2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>3769</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2023-07-12T00:34:53+00:00</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2023-07-14T08:12:27+00:00</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>chore(deps): bump semver from 5.7.1 to 5.7.2 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>3750</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2023-06-24T10:59:14+00:00</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2023-07-17T18:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>fix(deps): bump semver from 7.3.8 to 7.5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>3589</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2023-03-16T11:45:06+00:00</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2023-03-16T12:20:35+00:00</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>chore(deps): bump webpack from 5.73.0 to 5.76.2 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>3587</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2023-03-15T02:23:11+00:00</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>chore(deps): bump webpack from 5.73.0 to 5.76.1 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>3576</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2023-03-08T12:24:42+00:00</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2023-03-16T12:04:58+00:00</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>chore(deps): bump eta, @docusaurus/core, @docusaurus/plugin-sitemap and @docusaurus/preset-classic in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>3532</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2023-02-09T04:32:08+00:00</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2023-02-09T12:57:03+00:00</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>chore(deps): bump @sideway/formula from 3.0.0 to 3.0.1 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>3531</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2023-02-09T04:31:20+00:00</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2023-02-09T12:56:48+00:00</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>chore(deps): bump @sideway/formula from 3.0.0 to 3.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>3525</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2023-02-02T11:32:09+00:00</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2023-02-05T10:05:13+00:00</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>chore(deps): bump http-cache-semantics from 4.1.0 to 4.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>3524</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2023-02-02T11:30:41+00:00</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2023-02-03T17:42:34+00:00</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>chore(deps): bump http-cache-semantics from 4.1.0 to 4.1.1 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>3514</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2023-01-27T17:24:21+00:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2023-01-31T12:30:38+00:00</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>chore(deps): bump ua-parser-js from 0.7.32 to 0.7.33 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>3485</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2023-01-05T16:47:25+00:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2023-01-05T17:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>chore(deps): bump json5 from 1.0.1 to 1.0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>3479</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2023-01-01T14:56:16+00:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2023-01-01T15:47:57+00:00</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>chore(deps): bump json5 from 2.2.1 to 2.2.3 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>3473</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2022-12-26T18:17:38+00:00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>chore(deps): bump jsonwebtoken from 8.5.1 to 9.0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>3452</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2022-12-01T23:22:42+00:00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2022-12-13T09:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>chore(deps): bump decode-uri-component from 0.2.0 to 0.2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>3448</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2022-11-29T13:35:23+00:00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2022-11-29T18:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>chore(deps): bump minimatch, recursive-readdir and serve-handler in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>3430</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2022-11-16T06:24:36+00:00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2022-11-29T13:34:25+00:00</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>chore(deps): bump loader-utils from 2.0.3 to 2.0.4 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>3420</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2022-11-08T13:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2022-11-08T13:45:48+00:00</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>chore(deps): bump loader-utils from 2.0.2 to 2.0.3 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>3330</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2022-09-17T13:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2022-09-19T09:01:46+00:00</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>chore(deps): bump parse-url and git-url-parse</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>3299</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2022-08-18T19:59:35+00:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2022-08-31T11:38:25+00:00</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>chore(deps-dev): bump @actions/core from 1.8.2 to 1.9.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>3253</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2022-07-21T06:18:06+00:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2022-07-21T16:33:03+00:00</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>chore(deps): bump terser from 5.14.0 to 5.14.2 in /website</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>3128</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2022-05-12T18:58:59+00:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>chore(deps): bump @npmcli/git from 2.0.4 to 2.1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>3066</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2022-01-22T03:40:19+00:00</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>chore(deps): bump node-fetch from 2.6.1 to 3.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2982</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2021-08-31T18:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>chore(deps): bump tar from 6.1.0 to 6.1.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2961</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2021-08-03T19:28:11+00:00</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>chore(deps): bump tar from 6.1.0 to 6.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2924</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2021-06-08T02:31:43+00:00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>chore(deps): bump glob-parent from 5.1.1 to 5.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2777</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2020-12-10T18:35:34+00:00</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>chore(deps): bump ini from 1.3.5 to 1.3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2677</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2020-07-30T02:19:58+00:00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>chore(deps): bump dot-prop from 4.2.0 to 5.2.0 in /core/project</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2676</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2020-07-29T22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>chore(deps): bump dot-prop from 4.2.0 to 5.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2662</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2020-07-16T00:47:18+00:00</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>chore(deps): bump lodash from 4.17.15 to 4.17.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2493</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2020-03-13T21:26:05+00:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>chore(deps): bump acorn from 5.7.3 to 5.7.4</t>
         </is>
       </c>
     </row>
